--- a/backend/data/financials_by_company/1HLE.MI.xlsx
+++ b/backend/data/financials_by_company/1HLE.MI.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,55 +672,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44712</v>
       </c>
       <c r="B2" t="n">
-        <v>13808064.583343</v>
+        <v>7819330.653765</v>
       </c>
       <c r="C2" t="n">
-        <v>0.101411</v>
+        <v>0.275678</v>
       </c>
       <c r="D2" t="n">
-        <v>925265000</v>
+        <v>676125000</v>
       </c>
       <c r="E2" t="n">
-        <v>136160000</v>
+        <v>28364000</v>
       </c>
       <c r="F2" t="n">
-        <v>136160000</v>
+        <v>28364000</v>
       </c>
       <c r="G2" t="n">
-        <v>353104000</v>
+        <v>181261000</v>
       </c>
       <c r="H2" t="n">
-        <v>585461000</v>
+        <v>424921000</v>
       </c>
       <c r="I2" t="n">
-        <v>6268263000</v>
+        <v>4866619000</v>
       </c>
       <c r="J2" t="n">
-        <v>1061425000</v>
+        <v>704489000</v>
       </c>
       <c r="K2" t="n">
-        <v>475964000</v>
+        <v>279568000</v>
       </c>
       <c r="L2" t="n">
-        <v>-56769000</v>
+        <v>-26087000</v>
       </c>
       <c r="M2" t="n">
-        <v>63226000</v>
+        <v>25547000</v>
       </c>
       <c r="N2" t="n">
-        <v>43161000</v>
+        <v>8406000</v>
       </c>
       <c r="O2" t="n">
-        <v>230752064.583343</v>
+        <v>160716330.653765</v>
       </c>
       <c r="P2" t="n">
-        <v>353104000</v>
+        <v>181261000</v>
       </c>
       <c r="Q2" t="n">
-        <v>7696158000</v>
+        <v>6119356000</v>
       </c>
       <c r="R2" t="n">
         <v>111111112</v>
@@ -729,91 +729,97 @@
         <v>111111112</v>
       </c>
       <c r="T2" t="n">
-        <v>3.18</v>
+        <v>1.63</v>
       </c>
       <c r="U2" t="n">
-        <v>3.18</v>
+        <v>1.63</v>
       </c>
       <c r="V2" t="n">
-        <v>353104000</v>
+        <v>181261000</v>
       </c>
       <c r="W2" t="n">
-        <v>353104000</v>
+        <v>181261000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>353104000</v>
+        <v>181261000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-17777000</v>
+        <v>-2731000</v>
       </c>
       <c r="AA2" t="n">
-        <v>370882000</v>
+        <v>183993000</v>
       </c>
       <c r="AB2" t="n">
-        <v>370882000</v>
+        <v>183993000</v>
       </c>
       <c r="AC2" t="n">
-        <v>41856000</v>
+        <v>70028000</v>
       </c>
       <c r="AD2" t="n">
-        <v>412738000</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+        <v>254021000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>18280000</v>
+      </c>
       <c r="AF2" t="n">
-        <v>-3053000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>2001000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-1440000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>3053000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>-702000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>141000</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>-56769000</v>
+        <v>-26087000</v>
       </c>
       <c r="AK2" t="n">
-        <v>36704000</v>
+        <v>8946000</v>
       </c>
       <c r="AL2" t="n">
-        <v>63226000</v>
+        <v>25547000</v>
       </c>
       <c r="AM2" t="n">
-        <v>43161000</v>
+        <v>8406000</v>
       </c>
       <c r="AN2" t="n">
-        <v>328634000</v>
+        <v>206760000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1427895000</v>
+        <v>1252737000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-4658000</v>
+        <v>-4961000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>810724000</v>
+        <v>689389000</v>
       </c>
       <c r="AR2" t="n">
-        <v>641572000</v>
+        <v>573964000</v>
       </c>
       <c r="AS2" t="n">
-        <v>322796000</v>
+        <v>330952000</v>
       </c>
       <c r="AT2" t="n">
-        <v>318776000</v>
+        <v>243012000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1756529000</v>
+        <v>1459497000</v>
       </c>
       <c r="AV2" t="n">
-        <v>6268263000</v>
+        <v>4866619000</v>
       </c>
       <c r="AW2" t="n">
-        <v>8024792000</v>
+        <v>6326117000</v>
       </c>
       <c r="AX2" t="n">
-        <v>8024792000</v>
+        <v>6326117000</v>
       </c>
     </row>
     <row r="3">
@@ -966,55 +972,55 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44712</v>
+        <v>45657</v>
       </c>
       <c r="B4" t="n">
-        <v>7819330.653765</v>
+        <v>13808064.583343</v>
       </c>
       <c r="C4" t="n">
-        <v>0.275678</v>
+        <v>0.101411</v>
       </c>
       <c r="D4" t="n">
-        <v>676125000</v>
+        <v>925265000</v>
       </c>
       <c r="E4" t="n">
-        <v>28364000</v>
+        <v>136160000</v>
       </c>
       <c r="F4" t="n">
-        <v>28364000</v>
+        <v>136160000</v>
       </c>
       <c r="G4" t="n">
-        <v>181261000</v>
+        <v>353104000</v>
       </c>
       <c r="H4" t="n">
-        <v>424921000</v>
+        <v>585461000</v>
       </c>
       <c r="I4" t="n">
-        <v>4866619000</v>
+        <v>6268263000</v>
       </c>
       <c r="J4" t="n">
-        <v>704489000</v>
+        <v>1061425000</v>
       </c>
       <c r="K4" t="n">
-        <v>279568000</v>
+        <v>475964000</v>
       </c>
       <c r="L4" t="n">
-        <v>-26087000</v>
+        <v>-56766000</v>
       </c>
       <c r="M4" t="n">
-        <v>25547000</v>
+        <v>63226000</v>
       </c>
       <c r="N4" t="n">
-        <v>8406000</v>
+        <v>43161000</v>
       </c>
       <c r="O4" t="n">
-        <v>160716330.653765</v>
+        <v>230752064.583343</v>
       </c>
       <c r="P4" t="n">
-        <v>181261000</v>
+        <v>353104000</v>
       </c>
       <c r="Q4" t="n">
-        <v>6119356000</v>
+        <v>7696148000</v>
       </c>
       <c r="R4" t="n">
         <v>111111112</v>
@@ -1023,97 +1029,239 @@
         <v>111111112</v>
       </c>
       <c r="T4" t="n">
-        <v>1.63</v>
+        <v>3.18</v>
       </c>
       <c r="U4" t="n">
-        <v>1.63</v>
+        <v>3.18</v>
       </c>
       <c r="V4" t="n">
-        <v>181261000</v>
+        <v>353104000</v>
       </c>
       <c r="W4" t="n">
-        <v>181261000</v>
+        <v>353104000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>181261000</v>
+        <v>353104000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-2731000</v>
+        <v>-17777000</v>
       </c>
       <c r="AA4" t="n">
-        <v>183993000</v>
+        <v>370882000</v>
       </c>
       <c r="AB4" t="n">
-        <v>183993000</v>
+        <v>370882000</v>
       </c>
       <c r="AC4" t="n">
-        <v>70028000</v>
+        <v>41856000</v>
       </c>
       <c r="AD4" t="n">
-        <v>254021000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>18280000</v>
-      </c>
+        <v>412738000</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>2001000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-1440000</v>
-      </c>
+        <v>-3053000</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>-702000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>141000</v>
-      </c>
+        <v>3053000</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>-26087000</v>
+        <v>-56766000</v>
       </c>
       <c r="AK4" t="n">
-        <v>8946000</v>
+        <v>36701000</v>
       </c>
       <c r="AL4" t="n">
-        <v>25547000</v>
+        <v>63226000</v>
       </c>
       <c r="AM4" t="n">
-        <v>8406000</v>
+        <v>43161000</v>
       </c>
       <c r="AN4" t="n">
-        <v>206760000</v>
+        <v>328644000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1252737000</v>
+        <v>1427885000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-4961000</v>
+        <v>-6933000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>689389000</v>
+        <v>810724000</v>
       </c>
       <c r="AR4" t="n">
-        <v>573964000</v>
+        <v>643837000</v>
       </c>
       <c r="AS4" t="n">
-        <v>330952000</v>
+        <v>322796000</v>
       </c>
       <c r="AT4" t="n">
-        <v>243012000</v>
+        <v>321041000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1459497000</v>
+        <v>1756529000</v>
       </c>
       <c r="AV4" t="n">
-        <v>4866619000</v>
+        <v>6268263000</v>
       </c>
       <c r="AW4" t="n">
-        <v>6326117000</v>
+        <v>8024792000</v>
       </c>
       <c r="AX4" t="n">
-        <v>6326117000</v>
+        <v>8024792000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B5" t="n">
+        <v>535200</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>916075000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3568000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3568000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>83320000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>605525000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6148367000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>919643000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>314118000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-45726000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>56264000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>24587000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>80287200</v>
+      </c>
+      <c r="P5" t="n">
+        <v>83320000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>7564591000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>111111112</v>
+      </c>
+      <c r="S5" t="n">
+        <v>111111112</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V5" t="n">
+        <v>83320000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>83320000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>83320000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-9283000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>92704000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>92704000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>165150000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>257854000</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="n">
+        <v>9605000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-9605000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="n">
+        <v>-45726000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>14049000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>56264000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>24587000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>297533000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1416224000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1144000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>769383000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>655830000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>323646000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>332184000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1713757000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>6148367000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>7862124000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7862124000</v>
       </c>
     </row>
   </sheetData>
@@ -1127,7 +1275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC4"/>
+  <dimension ref="A1:CC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1534,7 +1682,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44712</v>
       </c>
       <c r="B2" t="n">
         <v>111111112</v>
@@ -1542,45 +1690,47 @@
       <c r="C2" t="n">
         <v>111111112</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>466168000</v>
+      </c>
       <c r="E2" t="n">
-        <v>958982000</v>
+        <v>1206230000</v>
       </c>
       <c r="F2" t="n">
-        <v>2484136000</v>
+        <v>2345177000</v>
       </c>
       <c r="G2" t="n">
-        <v>4000553000</v>
+        <v>3778585000</v>
       </c>
       <c r="H2" t="n">
-        <v>1269071000</v>
+        <v>1469430000</v>
       </c>
       <c r="I2" t="n">
-        <v>2484136000</v>
+        <v>2345177000</v>
       </c>
       <c r="J2" t="n">
-        <v>158859000</v>
+        <v>163933000</v>
       </c>
       <c r="K2" t="n">
-        <v>3200430000</v>
+        <v>2736288000</v>
       </c>
       <c r="L2" t="n">
-        <v>3921497000</v>
+        <v>3778585000</v>
       </c>
       <c r="M2" t="n">
-        <v>3247301000</v>
+        <v>2739140000</v>
       </c>
       <c r="N2" t="n">
-        <v>46871000</v>
+        <v>2852000</v>
       </c>
       <c r="O2" t="n">
-        <v>3200430000</v>
+        <v>2736288000</v>
       </c>
       <c r="P2" t="n">
         <v>-1000</v>
       </c>
       <c r="Q2" t="n">
-        <v>2856770000</v>
+        <v>2342436000</v>
       </c>
       <c r="R2" t="n">
         <v>250234000</v>
@@ -1592,182 +1742,172 @@
         <v>222222000</v>
       </c>
       <c r="U2" t="n">
-        <v>4235918000</v>
+        <v>3705833000</v>
       </c>
       <c r="V2" t="n">
-        <v>1614373000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1000</v>
-      </c>
+        <v>1666693000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>77115000</v>
+        <v>57706000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
+      <c r="Z2" t="n">
         <v>0</v>
       </c>
+      <c r="AA2" t="n">
+        <v>16000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>33761000</v>
+        <v>47771000</v>
       </c>
       <c r="AD2" t="n">
-        <v>840748000</v>
+        <v>1173709000</v>
       </c>
       <c r="AE2" t="n">
-        <v>119681000</v>
+        <v>131412000</v>
       </c>
       <c r="AF2" t="n">
-        <v>721067000</v>
+        <v>1042297000</v>
       </c>
       <c r="AG2" t="n">
-        <v>449131000</v>
+        <v>369710000</v>
       </c>
       <c r="AH2" t="n">
-        <v>2621545000</v>
+        <v>2039140000</v>
       </c>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>118234000</v>
+        <v>32521000</v>
       </c>
       <c r="AK2" t="n">
-        <v>39178000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>79056000</v>
-      </c>
+        <v>32521000</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>184862000</v>
+        <v>196506000</v>
       </c>
       <c r="AN2" t="n">
-        <v>153414000</v>
+        <v>144281000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1624720000</v>
+        <v>1162109000</v>
       </c>
       <c r="AP2" t="n">
-        <v>118324000</v>
+        <v>80280000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1506396000</v>
+        <v>1081829000</v>
       </c>
       <c r="AR2" t="n">
-        <v>7483219000</v>
+        <v>6444973000</v>
       </c>
       <c r="AS2" t="n">
-        <v>3592602000</v>
+        <v>2936404000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>19100000</v>
-      </c>
+        <v>9839000</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>58642000</v>
+        <v>33719000</v>
       </c>
       <c r="AW2" t="n">
-        <v>134906000</v>
+        <v>89778000</v>
       </c>
       <c r="AX2" t="n">
-        <v>77929000</v>
+        <v>121953000</v>
       </c>
       <c r="AY2" t="n">
-        <v>19411000</v>
+        <v>121953000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>58518000</v>
+        <v>39902000</v>
       </c>
       <c r="BA2" t="n">
-        <v>98349000</v>
+        <v>224182000</v>
       </c>
       <c r="BB2" t="n">
-        <v>716294000</v>
+        <v>391111000</v>
       </c>
       <c r="BC2" t="n">
-        <v>711460000</v>
+        <v>386035000</v>
       </c>
       <c r="BD2" t="n">
-        <v>4834000</v>
+        <v>5076000</v>
       </c>
       <c r="BE2" t="n">
-        <v>2323492000</v>
+        <v>1956470000</v>
       </c>
       <c r="BF2" t="n">
-        <v>-4390120000</v>
+        <v>-4215172000</v>
       </c>
       <c r="BG2" t="n">
-        <v>6713611000</v>
+        <v>6171642000</v>
       </c>
       <c r="BH2" t="n">
-        <v>380758000</v>
+        <v>424636000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1250799000</v>
+        <v>1353301000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>3802247000</v>
+        <v>3292327000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1279807000</v>
+        <v>1101378000</v>
       </c>
       <c r="BL2" t="n">
-        <v>3890616000</v>
+        <v>3508570000</v>
       </c>
       <c r="BM2" t="n">
-        <v>31272000</v>
+        <v>12652000</v>
       </c>
       <c r="BN2" t="n">
-        <v>4880000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
+        <v>14946000</v>
+      </c>
+      <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="n">
-        <v>93023000</v>
+        <v>64629000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1118106000</v>
+        <v>1136391000</v>
       </c>
       <c r="BR2" t="n">
-        <v>6315000</v>
+        <v>4485000</v>
       </c>
       <c r="BS2" t="n">
-        <v>228796000</v>
+        <v>234210000</v>
       </c>
       <c r="BT2" t="n">
-        <v>438096000</v>
+        <v>427142000</v>
       </c>
       <c r="BU2" t="n">
-        <v>444899000</v>
+        <v>470554000</v>
       </c>
       <c r="BV2" t="n">
-        <v>135462000</v>
+        <v>60509000</v>
       </c>
       <c r="BW2" t="n">
-        <v>143515000</v>
+        <v>139372000</v>
       </c>
       <c r="BX2" t="n">
-        <v>941371000</v>
+        <v>1071974000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1401520000</v>
+        <v>990688000</v>
       </c>
       <c r="BZ2" t="n">
-        <v>108353000</v>
+        <v>414559000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1293167000</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>289535000</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>1003633000</v>
-      </c>
+        <v>576129000</v>
+      </c>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -2012,7 +2152,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44712</v>
+        <v>45657</v>
       </c>
       <c r="B4" t="n">
         <v>111111112</v>
@@ -2020,47 +2160,45 @@
       <c r="C4" t="n">
         <v>111111112</v>
       </c>
-      <c r="D4" t="n">
-        <v>466168000</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>1206230000</v>
+        <v>958982000</v>
       </c>
       <c r="F4" t="n">
-        <v>2345177000</v>
+        <v>2484136000</v>
       </c>
       <c r="G4" t="n">
-        <v>3778585000</v>
+        <v>4000553000</v>
       </c>
       <c r="H4" t="n">
-        <v>1469430000</v>
+        <v>1269071000</v>
       </c>
       <c r="I4" t="n">
-        <v>2345177000</v>
+        <v>2484136000</v>
       </c>
       <c r="J4" t="n">
-        <v>163933000</v>
+        <v>158859000</v>
       </c>
       <c r="K4" t="n">
-        <v>2736288000</v>
+        <v>3200430000</v>
       </c>
       <c r="L4" t="n">
-        <v>3778585000</v>
+        <v>3921497000</v>
       </c>
       <c r="M4" t="n">
-        <v>2739140000</v>
+        <v>3247301000</v>
       </c>
       <c r="N4" t="n">
-        <v>2852000</v>
+        <v>46871000</v>
       </c>
       <c r="O4" t="n">
-        <v>2736288000</v>
+        <v>3200430000</v>
       </c>
       <c r="P4" t="n">
         <v>-1000</v>
       </c>
       <c r="Q4" t="n">
-        <v>2342436000</v>
+        <v>2856770000</v>
       </c>
       <c r="R4" t="n">
         <v>250234000</v>
@@ -2072,172 +2210,417 @@
         <v>222222000</v>
       </c>
       <c r="U4" t="n">
-        <v>3705833000</v>
+        <v>4235918000</v>
       </c>
       <c r="V4" t="n">
-        <v>1666693000</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>1614373000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1000</v>
+      </c>
       <c r="X4" t="n">
-        <v>57706000</v>
+        <v>77115000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="n">
         <v>0</v>
       </c>
-      <c r="AA4" t="n">
-        <v>16000</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>47771000</v>
+        <v>33761000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1173709000</v>
+        <v>840748000</v>
       </c>
       <c r="AE4" t="n">
-        <v>131412000</v>
+        <v>119681000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1042297000</v>
+        <v>721067000</v>
       </c>
       <c r="AG4" t="n">
-        <v>369710000</v>
+        <v>449131000</v>
       </c>
       <c r="AH4" t="n">
-        <v>2039140000</v>
+        <v>2621545000</v>
       </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>32521000</v>
+        <v>118234000</v>
       </c>
       <c r="AK4" t="n">
-        <v>32521000</v>
-      </c>
-      <c r="AL4" t="inlineStr"/>
+        <v>39178000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>79056000</v>
+      </c>
       <c r="AM4" t="n">
-        <v>196506000</v>
+        <v>184862000</v>
       </c>
       <c r="AN4" t="n">
-        <v>144281000</v>
+        <v>153414000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1162109000</v>
+        <v>1624720000</v>
       </c>
       <c r="AP4" t="n">
-        <v>80280000</v>
+        <v>118324000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1081829000</v>
+        <v>1506396000</v>
       </c>
       <c r="AR4" t="n">
-        <v>6444973000</v>
+        <v>7483219000</v>
       </c>
       <c r="AS4" t="n">
-        <v>2936404000</v>
+        <v>3592602000</v>
       </c>
       <c r="AT4" t="n">
-        <v>9839000</v>
-      </c>
-      <c r="AU4" t="inlineStr"/>
+        <v>-1000</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>19100000</v>
+      </c>
       <c r="AV4" t="n">
-        <v>33719000</v>
+        <v>58642000</v>
       </c>
       <c r="AW4" t="n">
-        <v>89778000</v>
+        <v>134906000</v>
       </c>
       <c r="AX4" t="n">
-        <v>121953000</v>
+        <v>77929000</v>
       </c>
       <c r="AY4" t="n">
-        <v>121953000</v>
+        <v>19411000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>39902000</v>
+        <v>58518000</v>
       </c>
       <c r="BA4" t="n">
-        <v>224182000</v>
+        <v>98349000</v>
       </c>
       <c r="BB4" t="n">
-        <v>391111000</v>
+        <v>716294000</v>
       </c>
       <c r="BC4" t="n">
-        <v>386035000</v>
+        <v>711460000</v>
       </c>
       <c r="BD4" t="n">
-        <v>5076000</v>
+        <v>4834000</v>
       </c>
       <c r="BE4" t="n">
-        <v>1956470000</v>
+        <v>2323491000</v>
       </c>
       <c r="BF4" t="n">
-        <v>-4215172000</v>
+        <v>-4390120000</v>
       </c>
       <c r="BG4" t="n">
-        <v>6171642000</v>
+        <v>6713611000</v>
       </c>
       <c r="BH4" t="n">
-        <v>424636000</v>
+        <v>380758000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1353301000</v>
+        <v>1250799000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>3292327000</v>
+        <v>3802247000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1101378000</v>
+        <v>1279807000</v>
       </c>
       <c r="BL4" t="n">
-        <v>3508570000</v>
+        <v>3890616000</v>
       </c>
       <c r="BM4" t="n">
-        <v>12652000</v>
+        <v>31272000</v>
       </c>
       <c r="BN4" t="n">
-        <v>14946000</v>
-      </c>
-      <c r="BO4" t="inlineStr"/>
+        <v>4880000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
       <c r="BP4" t="n">
-        <v>64629000</v>
+        <v>93023000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1136391000</v>
+        <v>1118106000</v>
       </c>
       <c r="BR4" t="n">
-        <v>4485000</v>
+        <v>6315000</v>
       </c>
       <c r="BS4" t="n">
-        <v>234210000</v>
+        <v>228796000</v>
       </c>
       <c r="BT4" t="n">
-        <v>427142000</v>
+        <v>438096000</v>
       </c>
       <c r="BU4" t="n">
-        <v>470554000</v>
+        <v>444899000</v>
       </c>
       <c r="BV4" t="n">
-        <v>60509000</v>
+        <v>135462000</v>
       </c>
       <c r="BW4" t="n">
-        <v>139372000</v>
+        <v>143515000</v>
       </c>
       <c r="BX4" t="n">
-        <v>1071974000</v>
+        <v>941371000</v>
       </c>
       <c r="BY4" t="n">
-        <v>990688000</v>
+        <v>1401520000</v>
       </c>
       <c r="BZ4" t="n">
-        <v>414559000</v>
+        <v>108353000</v>
       </c>
       <c r="CA4" t="n">
-        <v>576129000</v>
-      </c>
-      <c r="CB4" t="inlineStr"/>
-      <c r="CC4" t="inlineStr"/>
+        <v>1293167000</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>289535000</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>1003633000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B5" t="n">
+        <v>111111112</v>
+      </c>
+      <c r="C5" t="n">
+        <v>111111112</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>903612000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2284291000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3850047000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1188748000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2284291000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>134728000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3081163000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3713146000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3128235000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>47072000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3081163000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2830912000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>250234000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>222222000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>222222000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4197123000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1485140000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>93317000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>88829000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>726301000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>94318000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>631983000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>364418000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2711983000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>177311000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>40410000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>136901000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>220291000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>181170000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1681865000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>107454000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1574411000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>7325358000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3424627000</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>24647000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>94319000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>77438000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>73748000</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>23243000</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>50505000</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>95394000</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>796872000</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>792114000</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4758000</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>2088576000</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-4413259000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>6501835000</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>315957000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1303073000</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>3612822000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1269983000</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>3900731000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>34688000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>33117000</v>
+      </c>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="n">
+        <v>95055000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1129289000</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>2994000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>240209000</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>440914000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>445172000</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>94572000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>130650000</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>867442000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1496669000</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>94351000</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>1402318000</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>358214000</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>1044104000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2250,7 +2633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP4"/>
+  <dimension ref="A1:AP5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2462,122 +2845,122 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44712</v>
       </c>
       <c r="B2" t="n">
-        <v>173784000</v>
+        <v>-288013000</v>
       </c>
       <c r="C2" t="n">
-        <v>-680357000</v>
+        <v>-580485000</v>
       </c>
       <c r="D2" t="n">
-        <v>1293167000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38128000</v>
-      </c>
+        <v>576129000</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>1090450000</v>
+        <v>979495000</v>
       </c>
       <c r="G2" t="n">
-        <v>5308000</v>
+        <v>16069000</v>
       </c>
       <c r="H2" t="n">
-        <v>159281000</v>
+        <v>-419435000</v>
       </c>
       <c r="I2" t="n">
-        <v>-234472000</v>
+        <v>-149249000</v>
       </c>
       <c r="J2" t="n">
-        <v>-153178000</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>-18080000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-24242000</v>
+      </c>
       <c r="L2" t="n">
-        <v>-81294000</v>
+        <v>-106927000</v>
       </c>
       <c r="M2" t="n">
-        <v>-81294000</v>
+        <v>-106927000</v>
       </c>
       <c r="N2" t="n">
-        <v>-460388000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+        <v>-562658000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7644000</v>
+      </c>
       <c r="Q2" t="n">
-        <v>10414000</v>
+        <v>19552000</v>
       </c>
       <c r="R2" t="n">
-        <v>14134000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-3720000</v>
-      </c>
+        <v>19552000</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>194232000</v>
+        <v>-22819000</v>
       </c>
       <c r="U2" t="n">
-        <v>201873000</v>
+        <v>14102000</v>
       </c>
       <c r="V2" t="n">
-        <v>-7641000</v>
+        <v>-36921000</v>
       </c>
       <c r="W2" t="n">
-        <v>-224606000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
+        <v>-138439000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>6460000</v>
+      </c>
       <c r="Y2" t="n">
-        <v>-224606000</v>
+        <v>-144899000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-440428000</v>
+        <v>-421207000</v>
       </c>
       <c r="AA2" t="n">
-        <v>15323000</v>
+        <v>14379000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-455751000</v>
+        <v>-435586000</v>
       </c>
       <c r="AC2" t="n">
-        <v>854141000</v>
+        <v>292472000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-120174000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>39154000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-35436000</v>
-      </c>
+        <v>-37606000</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>10340000</v>
+        <v>9881000</v>
       </c>
       <c r="AH2" t="n">
-        <v>77863000</v>
+        <v>-331825000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-5031000</v>
+        <v>48055000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>84634000</v>
+        <v>-191066000</v>
       </c>
       <c r="AK2" t="n">
-        <v>91125000</v>
+        <v>-156311000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-121534000</v>
+        <v>-34420000</v>
       </c>
       <c r="AM2" t="n">
-        <v>585461000</v>
+        <v>424921000</v>
       </c>
       <c r="AN2" t="n">
-        <v>585461000</v>
+        <v>424921000</v>
       </c>
       <c r="AO2" t="n">
-        <v>5727000</v>
+        <v>7499000</v>
       </c>
       <c r="AP2" t="n">
-        <v>412738000</v>
+        <v>254021000</v>
       </c>
     </row>
     <row r="3">
@@ -2702,122 +3085,244 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44712</v>
+        <v>45657</v>
       </c>
       <c r="B4" t="n">
-        <v>-288013000</v>
+        <v>173784000</v>
       </c>
       <c r="C4" t="n">
-        <v>-580485000</v>
+        <v>-680357000</v>
       </c>
       <c r="D4" t="n">
-        <v>576129000</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>1293167000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>38128000</v>
+      </c>
       <c r="F4" t="n">
-        <v>979495000</v>
+        <v>1090450000</v>
       </c>
       <c r="G4" t="n">
-        <v>16069000</v>
+        <v>5308000</v>
       </c>
       <c r="H4" t="n">
-        <v>-419435000</v>
+        <v>159281000</v>
       </c>
       <c r="I4" t="n">
-        <v>-149249000</v>
+        <v>-234472000</v>
       </c>
       <c r="J4" t="n">
-        <v>-18080000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-24242000</v>
-      </c>
+        <v>-153178000</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-106927000</v>
+        <v>-81294000</v>
       </c>
       <c r="M4" t="n">
-        <v>-106927000</v>
+        <v>-81294000</v>
       </c>
       <c r="N4" t="n">
-        <v>-562658000</v>
-      </c>
-      <c r="O4" t="n">
+        <v>-460388000</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>10414000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>14134000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-3720000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>194232000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>201873000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-7641000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-224606000</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="n">
+        <v>-224606000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-440428000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>15323000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-455751000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>854141000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-120174000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>39154000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-35436000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>10340000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>77863000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-5031000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>84634000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>91125000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-121534000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>585461000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>585461000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>5727000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>412738000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B5" t="n">
+        <v>295473000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-616384000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1402318000</v>
+      </c>
+      <c r="E5" t="n">
         <v>1000</v>
       </c>
-      <c r="P4" t="n">
-        <v>7644000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>19552000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>19552000</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="n">
-        <v>-22819000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>14102000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-36921000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-138439000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>6460000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-144899000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-421207000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>14379000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-435586000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>292472000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-37606000</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="n">
-        <v>9881000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-331825000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>48055000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-191066000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>-156311000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-34420000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>424921000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>424921000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>7499000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>254021000</v>
+      <c r="F5" t="n">
+        <v>1293167000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-37648000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>146798000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-167631000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-56530000</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>-111101000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-111101000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-597428000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-6888000</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>6680000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6680000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-3041000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-3041000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-258830000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>-258830000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-335349000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>22205000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-357554000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>911857000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-86809000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>21894000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-31817000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>9126000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>117832000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>146849000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-50923000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>69186000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2789000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>605525000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>605525000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>15464000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>257854000</v>
       </c>
     </row>
   </sheetData>
@@ -3392,197 +3897,197 @@
       </c>
       <c r="DH1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EU1" t="inlineStr">
@@ -3602,10 +4107,8 @@
           <t>Lippstadt</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>59552</t>
-        </is>
+      <c r="C2" t="n">
+        <v>59552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3686,7 +4189,7 @@
         <v>6</v>
       </c>
       <c r="V2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="W2" t="n">
         <v>1735603200</v>
@@ -3739,7 +4242,7 @@
         <v>0.6506999999999999</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.339</v>
+        <v>0.315</v>
       </c>
       <c r="AN2" t="n">
         <v>53.63014</v>
@@ -3769,7 +4272,7 @@
         <v>8700000256</v>
       </c>
       <c r="AW2" t="n">
-        <v>8022222286</v>
+        <v>7888888952</v>
       </c>
       <c r="AX2" t="n">
         <v>76.2</v>
@@ -3790,7 +4293,7 @@
         <v>76.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>80.492615</v>
+        <v>80.123924</v>
       </c>
       <c r="BE2" t="n">
         <v>0.22</v>
@@ -3807,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>7962930688</v>
+        <v>7827326464</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.012150001</v>
@@ -3822,7 +4325,7 @@
         <v>0.8159999999999999</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.13294</v>
+        <v>0.13288</v>
       </c>
       <c r="BO2" t="n">
         <v>111111112</v>
@@ -3852,16 +4355,16 @@
         <v>1.46</v>
       </c>
       <c r="BX2" t="n">
-        <v>1.02</v>
+        <v>1.003</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.887</v>
+        <v>8.736000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>-0.054590583</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="CB2" t="n">
         <v>0.22</v>
@@ -3979,7 +4482,7 @@
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
+          <t>Hella KGaA</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
@@ -4021,100 +4524,100 @@
       <c r="DQ2" t="b">
         <v>0</v>
       </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>Hella KGaA</t>
-        </is>
-      </c>
-      <c r="DS2" t="b">
+      <c r="DR2" t="n">
+        <v>9.052924000000001</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="DT2" t="b">
         <v>0</v>
       </c>
-      <c r="DT2" t="n">
+      <c r="DU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
         <v>1762243200000</v>
       </c>
-      <c r="DU2" t="n">
+      <c r="DW2" t="n">
         <v>6.5</v>
       </c>
-      <c r="DV2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>78.3 - 87.0</t>
         </is>
       </c>
-      <c r="DW2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>Milan</t>
         </is>
       </c>
-      <c r="DX2" t="n">
+      <c r="DZ2" t="n">
         <v>0</v>
       </c>
-      <c r="DY2" t="n">
+      <c r="EA2" t="n">
         <v>2.100006</v>
       </c>
-      <c r="DZ2" t="n">
+      <c r="EB2" t="n">
         <v>0.027559137</v>
       </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>76.2 - 87.0</t>
         </is>
       </c>
-      <c r="EB2" t="n">
+      <c r="ED2" t="n">
         <v>-8.699997</v>
       </c>
-      <c r="EC2" t="n">
+      <c r="EE2" t="n">
         <v>-0.099999964</v>
       </c>
-      <c r="ED2" t="n">
+      <c r="EF2" t="n">
         <v>-5.4590583</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>1777476600</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1777476600</v>
       </c>
       <c r="EG2" t="n">
         <v>1777476600</v>
       </c>
       <c r="EH2" t="n">
+        <v>1777476600</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>1777476600</v>
+      </c>
+      <c r="EJ2" t="n">
         <v>1777449600</v>
       </c>
-      <c r="EI2" t="n">
+      <c r="EK2" t="n">
         <v>1777449600</v>
       </c>
-      <c r="EJ2" t="b">
+      <c r="EL2" t="b">
         <v>0</v>
       </c>
-      <c r="EK2" t="n">
+      <c r="EM2" t="n">
         <v>1.46</v>
       </c>
-      <c r="EL2" t="n">
+      <c r="EN2" t="n">
         <v>2.100006</v>
       </c>
-      <c r="EM2" t="n">
+      <c r="EO2" t="n">
         <v>0.027559137</v>
       </c>
-      <c r="EN2" t="n">
-        <v>-2.1926117</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>-0.027239911</v>
-      </c>
       <c r="EP2" t="n">
+        <v>-1.8239212</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>-0.022763753</v>
+      </c>
+      <c r="ER2" t="n">
         <v>20</v>
       </c>
-      <c r="EQ2" t="n">
+      <c r="ES2" t="n">
         <v>15</v>
       </c>
-      <c r="ER2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>9.052924000000001</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>78.3</v>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
       </c>
       <c r="EU2" t="inlineStr"/>
     </row>
